--- a/data/target_form/관인농협.xlsx
+++ b/data/target_form/관인농협.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\365건강\Desktop\사방넷발주\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skawl\PycharmProjects\365배포\data\target_form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2ACA3C-F18A-40B7-93D2-23673487C6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF302365-D4B8-402B-A0F4-5729601C54BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>수량</t>
   </si>
@@ -73,29 +73,8 @@
     <t>택배사코드(필수)</t>
   </si>
   <si>
-    <t>발신: 365건강농산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">수신: 관인농협 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수령인, 약어, 전화번호 주소 펼칠것</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -105,19 +84,11 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -140,14 +111,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -176,21 +139,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -208,29 +162,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -243,23 +188,17 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -281,9 +220,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -321,9 +260,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -356,26 +295,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -408,26 +330,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -604,20 +509,20 @@
   <sheetPr codeName="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.58203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="13.58203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="8" style="6" customWidth="1"/>
     <col min="8" max="8" width="111.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="70.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.58203125" style="2" customWidth="1"/>
     <col min="12" max="12" width="5.5" style="3" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
     <col min="14" max="14" width="14.75" style="1" customWidth="1"/>
@@ -625,81 +530,61 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="8" t="s">
+    <row r="1" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="8"/>
-    </row>
-    <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B1:I1"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -709,9 +594,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -721,9 +606,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" draft="1"/>
 </worksheet>
@@ -733,9 +618,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
